--- a/data/raw/API/2026.xlsx
+++ b/data/raw/API/2026.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/API/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A2D9F3A-3A11-4D7F-A6C7-A4D70B05A7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{4A2D9F3A-3A11-4D7F-A6C7-A4D70B05A7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85A03911-C403-4911-A3E7-3D8469C812BD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicadores" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Indicadores!$A$1:$Y$593</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -3317,7 +3320,7 @@
         <v>671</v>
       </c>
       <c r="O9">
-        <v>1</v>
+        <v>1700</v>
       </c>
       <c r="P9">
         <v>1800</v>
@@ -16206,7 +16209,7 @@
         <v>670</v>
       </c>
       <c r="O305">
-        <v>1</v>
+        <v>1700</v>
       </c>
       <c r="P305">
         <v>1800</v>
